--- a/output/rebalance_day_2026-03-05_153749/rebalance_day_report.xlsx
+++ b/output/rebalance_day_2026-03-05_153749/rebalance_day_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\rebalance_day_2026-03-05_153749\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191C9088-0B87-4492-AD7C-849CF7E12DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076ABEF5-FE3B-4AE6-A641-8A16A68F4598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rebalance_Day_Status" sheetId="1" r:id="rId1"/>
@@ -589,7 +589,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -629,7 +629,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,6 +934,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1722,6 +1725,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/output/rebalance_day_2026-03-05_153749/rebalance_day_report.xlsx
+++ b/output/rebalance_day_2026-03-05_153749/rebalance_day_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\rebalance_day_2026-03-05_153749\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076ABEF5-FE3B-4AE6-A641-8A16A68F4598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A0CDB8-260A-4136-84A5-4557F99D030D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14410" yWindow="6430" windowWidth="21600" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rebalance_Day_Status" sheetId="1" r:id="rId1"/>
@@ -71,13 +71,7 @@
     <t>Composite_Factor</t>
   </si>
   <si>
-    <t>beta_m1</t>
-  </si>
-  <si>
     <t>Composite_Method</t>
-  </si>
-  <si>
-    <t>多元回归beta加权 (M=3月, N=10日)</t>
   </si>
   <si>
     <t>Weight_Method</t>
@@ -583,6 +577,14 @@
   <si>
     <t>ASTS,BAC,CCJ,CSCO,CSX,EL,HROW,INTC,MO,ONDS,PAAS,PLTR,RKLB,SVM,TGT,TTMI,USB,WDC,WPM</t>
   </si>
+  <si>
+    <t>beta_m1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多元回归beta加权 (M=3月, N=10日)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1023,28 +1025,28 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -1052,7 +1054,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1068,42 +1070,42 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1122,57 +1124,57 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>40</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>41</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>42</v>
-      </c>
-      <c r="M1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1">
         <v>46086</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>49.819999694824219</v>
@@ -1195,13 +1197,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>46086</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>135.11500549316409</v>
@@ -1224,13 +1226,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>46086</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>39</v>
@@ -1253,13 +1255,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1">
         <v>46086</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>94.75</v>
@@ -1282,13 +1284,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1">
         <v>46086</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>137.91999816894531</v>
@@ -1311,13 +1313,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1">
         <v>46086</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>146.50999450683591</v>
@@ -1340,13 +1342,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1">
         <v>46086</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>10.5</v>
@@ -1369,13 +1371,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1">
         <v>46086</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>42.450000762939453</v>
@@ -1398,13 +1400,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1">
         <v>46086</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>80.014999389648438</v>
@@ -1427,13 +1429,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1">
         <v>46086</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>53.529998779296882</v>
@@ -1456,13 +1458,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1">
         <v>46086</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>370.98001098632813</v>
@@ -1485,13 +1487,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1">
         <v>46086</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F13">
         <v>95.470001220703125</v>
@@ -1514,13 +1516,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1">
         <v>46086</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F14">
         <v>44.869998931884773</v>
@@ -1543,13 +1545,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1">
         <v>46086</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>12.35000038146973</v>
@@ -1572,13 +1574,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1">
         <v>46086</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F16">
         <v>77.675003051757813</v>
@@ -1601,13 +1603,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1">
         <v>46086</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F17">
         <v>67.650001525878906</v>
@@ -1630,13 +1632,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1">
         <v>46086</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18">
         <v>98.495002746582031</v>
@@ -1659,13 +1661,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1">
         <v>46086</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F19">
         <v>92.300003051757813</v>
@@ -1688,13 +1690,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1">
         <v>46086</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <v>98</v>
@@ -1731,7 +1733,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1782,40 +1784,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>41</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
-      </c>
-      <c r="K1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1829,7 +1831,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2">
         <v>5.2631578947368432E-2</v>
@@ -1867,7 +1869,7 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3">
         <v>5.2631578947368432E-2</v>
@@ -1905,7 +1907,7 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4">
         <v>5.2631578947368432E-2</v>
@@ -1943,7 +1945,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>5.2631578947368432E-2</v>
@@ -1981,7 +1983,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6">
         <v>5.2631578947368432E-2</v>
@@ -2019,7 +2021,7 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7">
         <v>5.2631578947368432E-2</v>
@@ -2057,7 +2059,7 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E8">
         <v>5.2631578947368432E-2</v>
@@ -2095,7 +2097,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>5.2631578947368432E-2</v>
@@ -2133,7 +2135,7 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10">
         <v>5.2631578947368432E-2</v>
@@ -2171,7 +2173,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11">
         <v>5.2631578947368432E-2</v>
@@ -2209,7 +2211,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>5.2631578947368432E-2</v>
@@ -2247,7 +2249,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>5.2631578947368432E-2</v>
@@ -2285,7 +2287,7 @@
         <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14">
         <v>5.2631578947368432E-2</v>
@@ -2323,7 +2325,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15">
         <v>5.2631578947368432E-2</v>
@@ -2361,7 +2363,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>5.2631578947368432E-2</v>
@@ -2399,7 +2401,7 @@
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E17">
         <v>5.2631578947368432E-2</v>
@@ -2437,7 +2439,7 @@
         <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E18">
         <v>5.2631578947368432E-2</v>
@@ -2475,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E19">
         <v>5.2631578947368432E-2</v>
@@ -2513,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20">
         <v>5.2631578947368432E-2</v>
@@ -2551,7 +2553,7 @@
         <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21">
         <v>3.830593632802442E-16</v>
@@ -2589,7 +2591,7 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E22">
         <v>2.6765099151461951E-15</v>
@@ -2627,7 +2629,7 @@
         <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23">
         <v>9.6649278009113285E-2</v>
@@ -2665,7 +2667,7 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E24">
         <v>1.339234680219723E-15</v>
@@ -2703,7 +2705,7 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>6.8090236515175263E-16</v>
@@ -2741,7 +2743,7 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E26">
         <v>5.0935174767215555E-16</v>
@@ -2779,7 +2781,7 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E27">
         <v>0.1273172987057074</v>
@@ -2817,7 +2819,7 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E28">
         <v>0.39999999999999741</v>
@@ -2855,7 +2857,7 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E29">
         <v>3.4008666041775711E-17</v>
@@ -2893,7 +2895,7 @@
         <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <v>1.2569634899797229E-15</v>
@@ -2931,7 +2933,7 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E31">
         <v>3.9830686494261922E-16</v>
@@ -2969,7 +2971,7 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32">
         <v>3.8707867883477919E-16</v>
@@ -3007,7 +3009,7 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3045,7 +3047,7 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E34">
         <v>3.5088678303437522E-16</v>
@@ -3083,7 +3085,7 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35">
         <v>1.899915562515559E-15</v>
@@ -3121,7 +3123,7 @@
         <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>0.37603342328517092</v>
@@ -3159,7 +3161,7 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E37">
         <v>8.1107848642360367E-16</v>
@@ -3197,7 +3199,7 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E38">
         <v>9.2221536359042941E-17</v>
@@ -3235,7 +3237,7 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E39">
         <v>4.326503771952346E-16</v>
@@ -3273,7 +3275,7 @@
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E40">
         <v>5.5237982998300229E-17</v>
@@ -3311,7 +3313,7 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E41">
         <v>6.5727733058994126E-2</v>
@@ -3349,7 +3351,7 @@
         <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E42">
         <v>6.3398807707489055E-2</v>
@@ -3387,7 +3389,7 @@
         <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3425,7 +3427,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3463,7 +3465,7 @@
         <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E45">
         <v>1.8789814564058749E-16</v>
@@ -3501,7 +3503,7 @@
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>4.8651792665338998E-3</v>
@@ -3539,7 +3541,7 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E47">
         <v>0.1644420117830534</v>
@@ -3577,7 +3579,7 @@
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3615,7 +3617,7 @@
         <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E49">
         <v>0.3528486099557267</v>
@@ -3653,7 +3655,7 @@
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E50">
         <v>0.29612317456186171</v>
@@ -3691,7 +3693,7 @@
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3729,7 +3731,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3767,7 +3769,7 @@
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E53">
         <v>5.4581936006338702E-17</v>
@@ -3805,7 +3807,7 @@
         <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E54">
         <v>5.2594483666340577E-2</v>
@@ -3843,7 +3845,7 @@
         <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3881,7 +3883,7 @@
         <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E56">
         <v>3.2834554573955129E-16</v>
@@ -3919,7 +3921,7 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3957,7 +3959,7 @@
         <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3995,7 +3997,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E59">
         <v>4.7241158180061993E-18</v>
@@ -4033,7 +4035,7 @@
         <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E60">
         <v>0.25215176722181643</v>
@@ -4071,7 +4073,7 @@
         <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4109,7 +4111,7 @@
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E62">
         <v>0.13173931890629581</v>
@@ -4147,7 +4149,7 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E63">
         <v>1.7267826733895129E-17</v>
@@ -4185,7 +4187,7 @@
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E64">
         <v>4.2290687317676247E-2</v>
@@ -4223,7 +4225,7 @@
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E65">
         <v>2.022058358802362E-17</v>
@@ -4261,7 +4263,7 @@
         <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4299,7 +4301,7 @@
         <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E67">
         <v>0.28125076905866508</v>
@@ -4337,7 +4339,7 @@
         <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E68">
         <v>2.2751451874067751E-2</v>
@@ -4375,7 +4377,7 @@
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E69">
         <v>0.15451071288283169</v>
@@ -4413,7 +4415,7 @@
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E70">
         <v>1.9895322936277969E-17</v>
@@ -4451,7 +4453,7 @@
         <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E71">
         <v>2.3668231257974811E-18</v>
@@ -4489,7 +4491,7 @@
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4527,7 +4529,7 @@
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4565,7 +4567,7 @@
         <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E74">
         <v>2.765725784359177E-2</v>
@@ -4603,7 +4605,7 @@
         <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E75">
         <v>6.5263888585943833E-18</v>
@@ -4641,7 +4643,7 @@
         <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E76">
         <v>5.473548212274185E-17</v>
@@ -4679,7 +4681,7 @@
         <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E77">
         <v>8.7648034895055349E-2</v>
@@ -4717,7 +4719,7 @@
         <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4755,7 +4757,7 @@
         <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4793,7 +4795,7 @@
         <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4831,7 +4833,7 @@
         <v>31</v>
       </c>
       <c r="D81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E81">
         <v>0.10458791988685</v>
@@ -4869,7 +4871,7 @@
         <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4907,7 +4909,7 @@
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4945,7 +4947,7 @@
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E84">
         <v>1.312470225427342E-16</v>
@@ -4983,7 +4985,7 @@
         <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5021,7 +5023,7 @@
         <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E86">
         <v>0.4</v>
@@ -5059,7 +5061,7 @@
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E87">
         <v>0.1033513174632569</v>
@@ -5097,7 +5099,7 @@
         <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E88">
         <v>3.9295843857205188E-17</v>
@@ -5135,7 +5137,7 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E89">
         <v>1.1159770075545501E-18</v>
@@ -5173,7 +5175,7 @@
         <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E90">
         <v>7.4086917988773853E-17</v>
@@ -5211,7 +5213,7 @@
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E91">
         <v>2.8662273945112809E-2</v>
@@ -5249,7 +5251,7 @@
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E92">
         <v>2.3581377678924091E-17</v>
@@ -5287,7 +5289,7 @@
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E93">
         <v>0.33044086640654358</v>
@@ -5325,7 +5327,7 @@
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E94">
         <v>4.5863103004335968E-17</v>
@@ -5363,7 +5365,7 @@
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E95">
         <v>3.2957622298236407E-2</v>
@@ -5401,7 +5403,7 @@
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E96">
         <v>9.626242936429249E-18</v>
@@ -5439,7 +5441,7 @@
         <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E97">
         <v>1.006629220575561E-17</v>
@@ -5477,7 +5479,7 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5515,7 +5517,7 @@
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5553,7 +5555,7 @@
         <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E100">
         <v>1.9022849716763261E-2</v>
@@ -5591,7 +5593,7 @@
         <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E101">
         <v>4.6511584565812007E-3</v>
@@ -5629,7 +5631,7 @@
         <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E102">
         <v>9.7241714849455707E-2</v>
@@ -5667,7 +5669,7 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E103">
         <v>2.7764548334750531E-18</v>
@@ -5705,7 +5707,7 @@
         <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5743,7 +5745,7 @@
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E105">
         <v>2.6906941193092359E-17</v>
@@ -5781,7 +5783,7 @@
         <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E106">
         <v>8.0018433038745521E-2</v>
@@ -5819,7 +5821,7 @@
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5857,7 +5859,7 @@
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E108">
         <v>0.28429044747967669</v>
@@ -5895,7 +5897,7 @@
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E109">
         <v>0.18255960898867321</v>
@@ -5933,7 +5935,7 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E110">
         <v>0.26275711134252888</v>
@@ -5971,7 +5973,7 @@
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6009,7 +6011,7 @@
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E112">
         <v>6.9458676127575392E-2</v>
@@ -6047,7 +6049,7 @@
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6085,7 +6087,7 @@
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E114">
         <v>8.2761564284461783E-17</v>
@@ -6123,7 +6125,7 @@
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6161,7 +6163,7 @@
         <v>32</v>
       </c>
       <c r="D116" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6199,7 +6201,7 @@
         <v>32</v>
       </c>
       <c r="D117" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E117">
         <v>2.1546378858015989E-17</v>
@@ -6237,7 +6239,7 @@
         <v>32</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E118">
         <v>5.6057411466515274E-18</v>
@@ -6275,7 +6277,7 @@
         <v>32</v>
       </c>
       <c r="D119" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E119">
         <v>3.8091823031139102E-2</v>
@@ -6313,7 +6315,7 @@
         <v>32</v>
       </c>
       <c r="D120" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6351,7 +6353,7 @@
         <v>32</v>
       </c>
       <c r="D121" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E121">
         <v>0.22250607162381739</v>
@@ -6389,7 +6391,7 @@
         <v>32</v>
       </c>
       <c r="D122" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E122">
         <v>0.244839563189552</v>
@@ -6427,7 +6429,7 @@
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E123">
         <v>2.119673667414533E-17</v>
@@ -6465,7 +6467,7 @@
         <v>32</v>
       </c>
       <c r="D124" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6503,7 +6505,7 @@
         <v>32</v>
       </c>
       <c r="D125" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E125">
         <v>0.39999999999999991</v>
@@ -6541,7 +6543,7 @@
         <v>32</v>
       </c>
       <c r="D126" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E126">
         <v>9.4562542155491619E-2</v>
@@ -6579,7 +6581,7 @@
         <v>32</v>
       </c>
       <c r="D127" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6617,7 +6619,7 @@
         <v>32</v>
       </c>
       <c r="D128" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E128">
         <v>5.7099730195434748E-18</v>
@@ -6655,7 +6657,7 @@
         <v>32</v>
       </c>
       <c r="D129" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E129">
         <v>4.986248851382289E-18</v>
@@ -6693,7 +6695,7 @@
         <v>32</v>
       </c>
       <c r="D130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6731,7 +6733,7 @@
         <v>32</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E131">
         <v>2.6603466166815611E-17</v>
@@ -6769,7 +6771,7 @@
         <v>32</v>
       </c>
       <c r="D132" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E132">
         <v>2.288577027830061E-17</v>
@@ -6807,7 +6809,7 @@
         <v>32</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E133">
         <v>2.9722899544632958E-17</v>
@@ -6845,7 +6847,7 @@
         <v>32</v>
       </c>
       <c r="D134" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E134">
         <v>4.7764379475408797E-17</v>
@@ -6883,7 +6885,7 @@
         <v>31</v>
       </c>
       <c r="D135" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -6921,7 +6923,7 @@
         <v>31</v>
       </c>
       <c r="D136" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E136">
         <v>8.3811369031971243E-17</v>
@@ -6959,7 +6961,7 @@
         <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E137">
         <v>3.778072973030961E-2</v>
@@ -6997,7 +6999,7 @@
         <v>31</v>
       </c>
       <c r="D138" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E138">
         <v>0.19288053782189599</v>
@@ -7035,7 +7037,7 @@
         <v>31</v>
       </c>
       <c r="D139" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -7073,7 +7075,7 @@
         <v>31</v>
       </c>
       <c r="D140" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E140">
         <v>3.4406061848370418E-17</v>
@@ -7111,7 +7113,7 @@
         <v>31</v>
       </c>
       <c r="D141" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E141">
         <v>0.19647553899337111</v>
@@ -7149,7 +7151,7 @@
         <v>31</v>
       </c>
       <c r="D142" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E142">
         <v>2.6590941661193759E-2</v>
@@ -7187,7 +7189,7 @@
         <v>31</v>
       </c>
       <c r="D143" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E143">
         <v>0.4</v>
@@ -7225,7 +7227,7 @@
         <v>31</v>
       </c>
       <c r="D144" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E144">
         <v>0.14627225179322931</v>
@@ -7263,7 +7265,7 @@
         <v>31</v>
       </c>
       <c r="D145" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E145">
         <v>1.7271573279201801E-17</v>
@@ -7301,7 +7303,7 @@
         <v>31</v>
       </c>
       <c r="D146" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E146">
         <v>3.0106504710268601E-17</v>
@@ -7339,7 +7341,7 @@
         <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E147">
         <v>2.9559887339391252E-18</v>
@@ -7377,7 +7379,7 @@
         <v>31</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E148">
         <v>2.177737845928489E-17</v>
@@ -7415,7 +7417,7 @@
         <v>31</v>
       </c>
       <c r="D149" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -7453,7 +7455,7 @@
         <v>31</v>
       </c>
       <c r="D150" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E150">
         <v>7.7055017775571706E-17</v>
@@ -7491,7 +7493,7 @@
         <v>31</v>
       </c>
       <c r="D151" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E151">
         <v>2.072784650585057E-18</v>
@@ -7529,7 +7531,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -7567,7 +7569,7 @@
         <v>31</v>
       </c>
       <c r="D153" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -7605,7 +7607,7 @@
         <v>32</v>
       </c>
       <c r="D154" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -7643,7 +7645,7 @@
         <v>32</v>
       </c>
       <c r="D155" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E155">
         <v>0.11534726187534659</v>
@@ -7681,7 +7683,7 @@
         <v>32</v>
       </c>
       <c r="D156" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E156">
         <v>9.4399510474179158E-18</v>
@@ -7719,7 +7721,7 @@
         <v>32</v>
       </c>
       <c r="D157" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E157">
         <v>0.23088646848288749</v>
@@ -7757,7 +7759,7 @@
         <v>32</v>
       </c>
       <c r="D158" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -7795,7 +7797,7 @@
         <v>32</v>
       </c>
       <c r="D159" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E159">
         <v>1.196728259188092E-17</v>
@@ -7833,7 +7835,7 @@
         <v>32</v>
       </c>
       <c r="D160" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E160">
         <v>0.39999999999999991</v>
@@ -7871,7 +7873,7 @@
         <v>32</v>
       </c>
       <c r="D161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E161">
         <v>5.1620343849210261E-17</v>
@@ -7909,7 +7911,7 @@
         <v>32</v>
       </c>
       <c r="D162" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E162">
         <v>0.20256266434869391</v>
@@ -7947,7 +7949,7 @@
         <v>32</v>
       </c>
       <c r="D163" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E163">
         <v>4.1759809606592597E-2</v>
@@ -7985,7 +7987,7 @@
         <v>32</v>
       </c>
       <c r="D164" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -8023,7 +8025,7 @@
         <v>32</v>
       </c>
       <c r="D165" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -8061,7 +8063,7 @@
         <v>32</v>
       </c>
       <c r="D166" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E166">
         <v>9.4437956864792758E-3</v>
@@ -8099,7 +8101,7 @@
         <v>32</v>
       </c>
       <c r="D167" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E167">
         <v>4.0372409373829991E-17</v>
@@ -8137,7 +8139,7 @@
         <v>32</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -8175,7 +8177,7 @@
         <v>32</v>
       </c>
       <c r="D169" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8213,7 +8215,7 @@
         <v>32</v>
       </c>
       <c r="D170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8251,7 +8253,7 @@
         <v>32</v>
       </c>
       <c r="D171" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E171">
         <v>5.5601410566485948E-18</v>
@@ -8289,7 +8291,7 @@
         <v>32</v>
       </c>
       <c r="D172" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -8327,7 +8329,7 @@
         <v>31</v>
       </c>
       <c r="D173" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -8365,7 +8367,7 @@
         <v>31</v>
       </c>
       <c r="D174" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -8403,7 +8405,7 @@
         <v>31</v>
       </c>
       <c r="D175" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E175">
         <v>3.7156961741479187E-18</v>
@@ -8441,7 +8443,7 @@
         <v>31</v>
       </c>
       <c r="D176" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E176">
         <v>0.36772458441371081</v>
@@ -8479,7 +8481,7 @@
         <v>31</v>
       </c>
       <c r="D177" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -8517,7 +8519,7 @@
         <v>31</v>
       </c>
       <c r="D178" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E178">
         <v>0.36163753675044868</v>
@@ -8555,7 +8557,7 @@
         <v>31</v>
       </c>
       <c r="D179" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E179">
         <v>1.2013242115964811E-16</v>
@@ -8593,7 +8595,7 @@
         <v>31</v>
       </c>
       <c r="D180" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E180">
         <v>0.16061129937375071</v>
@@ -8631,7 +8633,7 @@
         <v>31</v>
       </c>
       <c r="D181" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E181">
         <v>3.199010837456479E-17</v>
@@ -8669,7 +8671,7 @@
         <v>31</v>
       </c>
       <c r="D182" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -8707,7 +8709,7 @@
         <v>31</v>
       </c>
       <c r="D183" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -8745,7 +8747,7 @@
         <v>31</v>
       </c>
       <c r="D184" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E184">
         <v>1.663476408431662E-16</v>
@@ -8783,7 +8785,7 @@
         <v>31</v>
       </c>
       <c r="D185" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E185">
         <v>3.2491283339676202E-17</v>
@@ -8821,7 +8823,7 @@
         <v>31</v>
       </c>
       <c r="D186" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E186">
         <v>1.405111186594169E-2</v>
@@ -8859,7 +8861,7 @@
         <v>31</v>
       </c>
       <c r="D187" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E187">
         <v>9.5975467596147779E-2</v>
@@ -8897,7 +8899,7 @@
         <v>31</v>
       </c>
       <c r="D188" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -8935,7 +8937,7 @@
         <v>31</v>
       </c>
       <c r="D189" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -8973,7 +8975,7 @@
         <v>31</v>
       </c>
       <c r="D190" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -9011,7 +9013,7 @@
         <v>31</v>
       </c>
       <c r="D191" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -9049,7 +9051,7 @@
         <v>33</v>
       </c>
       <c r="D192" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E192">
         <v>2.2271726507941932E-3</v>
@@ -9087,7 +9089,7 @@
         <v>33</v>
       </c>
       <c r="D193" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E193">
         <v>6.1922898337432732E-2</v>
@@ -9125,7 +9127,7 @@
         <v>33</v>
       </c>
       <c r="D194" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -9163,7 +9165,7 @@
         <v>33</v>
       </c>
       <c r="D195" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E195">
         <v>3.6873633320484822E-2</v>
@@ -9201,7 +9203,7 @@
         <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E196">
         <v>5.4191280121831983E-17</v>
@@ -9239,7 +9241,7 @@
         <v>33</v>
       </c>
       <c r="D197" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -9277,7 +9279,7 @@
         <v>33</v>
       </c>
       <c r="D198" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E198">
         <v>0.20392248430506191</v>
@@ -9315,7 +9317,7 @@
         <v>33</v>
       </c>
       <c r="D199" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -9353,7 +9355,7 @@
         <v>33</v>
       </c>
       <c r="D200" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E200">
         <v>9.3111302001570509E-18</v>
@@ -9391,7 +9393,7 @@
         <v>33</v>
       </c>
       <c r="D201" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E201">
         <v>0.15492302922640641</v>
@@ -9429,7 +9431,7 @@
         <v>33</v>
       </c>
       <c r="D202" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -9467,7 +9469,7 @@
         <v>33</v>
       </c>
       <c r="D203" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E203">
         <v>0.3543444708921592</v>
@@ -9505,7 +9507,7 @@
         <v>33</v>
       </c>
       <c r="D204" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>5.988243684953428E-2</v>
@@ -9543,7 +9545,7 @@
         <v>33</v>
       </c>
       <c r="D205" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E205">
         <v>1.382019681950703E-17</v>
@@ -9581,7 +9583,7 @@
         <v>33</v>
       </c>
       <c r="D206" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E206">
         <v>0.12590387441812639</v>
@@ -9619,7 +9621,7 @@
         <v>33</v>
       </c>
       <c r="D207" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E207">
         <v>2.5803102136798789E-17</v>
@@ -9657,7 +9659,7 @@
         <v>33</v>
       </c>
       <c r="D208" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E208">
         <v>4.9569304543809842E-17</v>
@@ -9695,7 +9697,7 @@
         <v>33</v>
       </c>
       <c r="D209" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E209">
         <v>1.36940633659593E-18</v>
@@ -9733,7 +9735,7 @@
         <v>33</v>
       </c>
       <c r="D210" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -9771,7 +9773,7 @@
         <v>30</v>
       </c>
       <c r="D211" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E211">
         <v>9.5637421792770572E-2</v>
@@ -9809,7 +9811,7 @@
         <v>30</v>
       </c>
       <c r="D212" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E212">
         <v>0.16560792823286771</v>
@@ -9847,7 +9849,7 @@
         <v>30</v>
       </c>
       <c r="D213" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E213">
         <v>3.433153374844215E-17</v>
@@ -9885,7 +9887,7 @@
         <v>30</v>
       </c>
       <c r="D214" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E214">
         <v>2.7121589301413549E-17</v>
@@ -9923,7 +9925,7 @@
         <v>30</v>
       </c>
       <c r="D215" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -9961,7 +9963,7 @@
         <v>30</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E216">
         <v>4.6064686374000667E-17</v>
@@ -9999,7 +10001,7 @@
         <v>30</v>
       </c>
       <c r="D217" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -10037,7 +10039,7 @@
         <v>30</v>
       </c>
       <c r="D218" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -10075,7 +10077,7 @@
         <v>30</v>
       </c>
       <c r="D219" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E219">
         <v>0.39353061645582738</v>
@@ -10113,7 +10115,7 @@
         <v>30</v>
       </c>
       <c r="D220" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E220">
         <v>0.26195070836648288</v>
@@ -10151,7 +10153,7 @@
         <v>30</v>
       </c>
       <c r="D221" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E221">
         <v>1.3729998405323061E-17</v>
@@ -10189,7 +10191,7 @@
         <v>30</v>
       </c>
       <c r="D222" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E222">
         <v>2.5637587577824009E-17</v>
@@ -10227,7 +10229,7 @@
         <v>30</v>
       </c>
       <c r="D223" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -10265,7 +10267,7 @@
         <v>30</v>
       </c>
       <c r="D224" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -10303,7 +10305,7 @@
         <v>30</v>
       </c>
       <c r="D225" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -10341,7 +10343,7 @@
         <v>30</v>
       </c>
       <c r="D226" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -10379,7 +10381,7 @@
         <v>30</v>
       </c>
       <c r="D227" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E227">
         <v>8.3273325152051436E-2</v>
@@ -10417,7 +10419,7 @@
         <v>30</v>
       </c>
       <c r="D228" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E228">
         <v>1.1770449137274721E-17</v>
@@ -10455,7 +10457,7 @@
         <v>30</v>
       </c>
       <c r="D229" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -10493,7 +10495,7 @@
         <v>32</v>
       </c>
       <c r="D230" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -10531,7 +10533,7 @@
         <v>32</v>
       </c>
       <c r="D231" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E231">
         <v>3.604201455690916E-3</v>
@@ -10569,7 +10571,7 @@
         <v>32</v>
       </c>
       <c r="D232" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E232">
         <v>1.3012762018432001E-17</v>
@@ -10607,7 +10609,7 @@
         <v>32</v>
       </c>
       <c r="D233" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -10645,7 +10647,7 @@
         <v>32</v>
       </c>
       <c r="D234" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -10683,7 +10685,7 @@
         <v>32</v>
       </c>
       <c r="D235" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E235">
         <v>6.9517873930327295E-2</v>
@@ -10721,7 +10723,7 @@
         <v>32</v>
       </c>
       <c r="D236" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E236">
         <v>0.12601306015077821</v>
@@ -10759,7 +10761,7 @@
         <v>32</v>
       </c>
       <c r="D237" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E237">
         <v>9.7089150397382959E-2</v>
@@ -10797,7 +10799,7 @@
         <v>32</v>
       </c>
       <c r="D238" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E238">
         <v>5.019760550676753E-2</v>
@@ -10835,7 +10837,7 @@
         <v>32</v>
       </c>
       <c r="D239" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E239">
         <v>0.23239697012881841</v>
@@ -10873,7 +10875,7 @@
         <v>32</v>
       </c>
       <c r="D240" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E240">
         <v>0.13079339163514539</v>
@@ -10911,7 +10913,7 @@
         <v>32</v>
       </c>
       <c r="D241" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -10949,7 +10951,7 @@
         <v>32</v>
       </c>
       <c r="D242" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E242">
         <v>2.3829367486240901E-17</v>
@@ -10987,7 +10989,7 @@
         <v>32</v>
       </c>
       <c r="D243" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E243">
         <v>7.2084634787433925E-18</v>
@@ -11025,7 +11027,7 @@
         <v>32</v>
       </c>
       <c r="D244" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E244">
         <v>8.1863630163484822E-18</v>
@@ -11063,7 +11065,7 @@
         <v>32</v>
       </c>
       <c r="D245" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E245">
         <v>0.270675191117703</v>
@@ -11101,7 +11103,7 @@
         <v>32</v>
       </c>
       <c r="D246" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E246">
         <v>1.8156914665217919E-2</v>
@@ -11139,7 +11141,7 @@
         <v>32</v>
       </c>
       <c r="D247" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E247">
         <v>1.5556410121683199E-3</v>
@@ -11177,7 +11179,7 @@
         <v>32</v>
       </c>
       <c r="D248" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -11215,7 +11217,7 @@
         <v>31</v>
       </c>
       <c r="D249" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -11253,7 +11255,7 @@
         <v>31</v>
       </c>
       <c r="D250" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E250">
         <v>2.5061925934892891E-18</v>
@@ -11291,7 +11293,7 @@
         <v>31</v>
       </c>
       <c r="D251" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E251">
         <v>2.6806720817267919E-17</v>
@@ -11329,7 +11331,7 @@
         <v>31</v>
       </c>
       <c r="D252" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E252">
         <v>3.191538828157768E-18</v>
@@ -11367,7 +11369,7 @@
         <v>31</v>
       </c>
       <c r="D253" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -11405,7 +11407,7 @@
         <v>31</v>
       </c>
       <c r="D254" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E254">
         <v>0.1122489574387199</v>
@@ -11443,7 +11445,7 @@
         <v>31</v>
       </c>
       <c r="D255" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E255">
         <v>4.0260823786922223E-2</v>
@@ -11481,7 +11483,7 @@
         <v>31</v>
       </c>
       <c r="D256" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E256">
         <v>0.1664058440746819</v>
@@ -11519,7 +11521,7 @@
         <v>31</v>
       </c>
       <c r="D257" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E257">
         <v>9.5581931233579248E-2</v>
@@ -11557,7 +11559,7 @@
         <v>31</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E258">
         <v>3.5542573758077299E-18</v>
@@ -11595,7 +11597,7 @@
         <v>31</v>
       </c>
       <c r="D259" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -11633,7 +11635,7 @@
         <v>31</v>
       </c>
       <c r="D260" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E260">
         <v>0.15373854845197721</v>
@@ -11671,7 +11673,7 @@
         <v>31</v>
       </c>
       <c r="D261" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E261">
         <v>1.6918784371723419E-2</v>
@@ -11709,7 +11711,7 @@
         <v>31</v>
       </c>
       <c r="D262" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E262">
         <v>6.8675652389016831E-18</v>
@@ -11747,7 +11749,7 @@
         <v>31</v>
       </c>
       <c r="D263" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E263">
         <v>0.2711622582460893</v>
@@ -11785,7 +11787,7 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E264">
         <v>8.4390963826232807E-18</v>
@@ -11823,7 +11825,7 @@
         <v>31</v>
       </c>
       <c r="D265" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E265">
         <v>0.1009217306062074</v>
@@ -11861,7 +11863,7 @@
         <v>31</v>
       </c>
       <c r="D266" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E266">
         <v>4.2761121790099381E-2</v>
@@ -11899,7 +11901,7 @@
         <v>31</v>
       </c>
       <c r="D267" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E267">
         <v>1.10094945166985E-17</v>
@@ -11937,7 +11939,7 @@
         <v>32</v>
       </c>
       <c r="D268" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E268">
         <v>2.6911544560942249E-17</v>
@@ -11975,7 +11977,7 @@
         <v>32</v>
       </c>
       <c r="D269" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E269">
         <v>5.8425257759235082E-18</v>
@@ -12013,7 +12015,7 @@
         <v>32</v>
       </c>
       <c r="D270" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E270">
         <v>6.6799804969336062E-18</v>
@@ -12051,7 +12053,7 @@
         <v>32</v>
       </c>
       <c r="D271" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -12089,7 +12091,7 @@
         <v>32</v>
       </c>
       <c r="D272" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E272">
         <v>0.10670448089842439</v>
@@ -12127,7 +12129,7 @@
         <v>32</v>
       </c>
       <c r="D273" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E273">
         <v>1.097321381515733E-17</v>
@@ -12165,7 +12167,7 @@
         <v>32</v>
       </c>
       <c r="D274" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E274">
         <v>2.8024615273423439E-2</v>
@@ -12203,7 +12205,7 @@
         <v>32</v>
       </c>
       <c r="D275" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E275">
         <v>8.7094906787545362E-2</v>
@@ -12241,7 +12243,7 @@
         <v>32</v>
       </c>
       <c r="D276" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E276">
         <v>1.249056877795307E-17</v>
@@ -12279,7 +12281,7 @@
         <v>32</v>
       </c>
       <c r="D277" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E277">
         <v>0.14711975982655251</v>
@@ -12317,7 +12319,7 @@
         <v>32</v>
       </c>
       <c r="D278" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E278">
         <v>7.9244640155946233E-2</v>
@@ -12355,7 +12357,7 @@
         <v>32</v>
       </c>
       <c r="D279" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E279">
         <v>0.15757764527872689</v>
@@ -12393,7 +12395,7 @@
         <v>32</v>
       </c>
       <c r="D280" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E280">
         <v>0.2146756643897455</v>
@@ -12431,7 +12433,7 @@
         <v>32</v>
       </c>
       <c r="D281" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E281">
         <v>1.9196709318297421E-17</v>
@@ -12469,7 +12471,7 @@
         <v>32</v>
       </c>
       <c r="D282" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E282">
         <v>8.1436909330859283E-3</v>
@@ -12507,7 +12509,7 @@
         <v>32</v>
       </c>
       <c r="D283" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E283">
         <v>6.8373525496484747E-2</v>
@@ -12545,7 +12547,7 @@
         <v>32</v>
       </c>
       <c r="D284" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E284">
         <v>4.8935993709916178E-2</v>
@@ -12583,7 +12585,7 @@
         <v>32</v>
       </c>
       <c r="D285" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E285">
         <v>5.4105077250148799E-2</v>
@@ -12621,7 +12623,7 @@
         <v>32</v>
       </c>
       <c r="D286" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -12659,7 +12661,7 @@
         <v>31</v>
       </c>
       <c r="D287" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E287">
         <v>4.0278065345082028E-17</v>
@@ -12697,7 +12699,7 @@
         <v>31</v>
       </c>
       <c r="D288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E288">
         <v>2.5202149433376369E-17</v>
@@ -12735,7 +12737,7 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E289">
         <v>6.3775612663218059E-2</v>
@@ -12773,7 +12775,7 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -12811,7 +12813,7 @@
         <v>31</v>
       </c>
       <c r="D291" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E291">
         <v>0.25564543489050617</v>
@@ -12849,7 +12851,7 @@
         <v>31</v>
       </c>
       <c r="D292" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E292">
         <v>7.8752624096609902E-18</v>
@@ -12887,7 +12889,7 @@
         <v>31</v>
       </c>
       <c r="D293" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -12925,7 +12927,7 @@
         <v>31</v>
       </c>
       <c r="D294" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E294">
         <v>4.6400427705943922E-2</v>
@@ -12963,7 +12965,7 @@
         <v>31</v>
       </c>
       <c r="D295" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E295">
         <v>6.5033113759392969E-2</v>
@@ -13001,7 +13003,7 @@
         <v>31</v>
       </c>
       <c r="D296" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E296">
         <v>1.2069202687812661E-17</v>
@@ -13039,7 +13041,7 @@
         <v>31</v>
       </c>
       <c r="D297" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E297">
         <v>8.0162867334772972E-2</v>
@@ -13077,7 +13079,7 @@
         <v>31</v>
       </c>
       <c r="D298" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E298">
         <v>0.1065316796515479</v>
@@ -13115,7 +13117,7 @@
         <v>31</v>
       </c>
       <c r="D299" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E299">
         <v>0.168799435249607</v>
@@ -13153,7 +13155,7 @@
         <v>31</v>
       </c>
       <c r="D300" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E300">
         <v>6.091524031827826E-2</v>
@@ -13191,7 +13193,7 @@
         <v>31</v>
       </c>
       <c r="D301" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E301">
         <v>2.4814082545294659E-17</v>
@@ -13229,7 +13231,7 @@
         <v>31</v>
       </c>
       <c r="D302" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E302">
         <v>0.1073195229954681</v>
@@ -13267,7 +13269,7 @@
         <v>31</v>
       </c>
       <c r="D303" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E303">
         <v>4.541666543126463E-2</v>
@@ -13305,7 +13307,7 @@
         <v>31</v>
       </c>
       <c r="D304" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -13343,7 +13345,7 @@
         <v>31</v>
       </c>
       <c r="D305" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -13381,7 +13383,7 @@
         <v>32</v>
       </c>
       <c r="D306" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E306">
         <v>0.1815582018411098</v>
@@ -13419,7 +13421,7 @@
         <v>32</v>
       </c>
       <c r="D307" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E307">
         <v>2.2165970673888221E-17</v>
@@ -13457,7 +13459,7 @@
         <v>32</v>
       </c>
       <c r="D308" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E308">
         <v>2.4772588550790169E-2</v>
@@ -13495,7 +13497,7 @@
         <v>32</v>
       </c>
       <c r="D309" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -13533,7 +13535,7 @@
         <v>32</v>
       </c>
       <c r="D310" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E310">
         <v>0.33394596521988618</v>
@@ -13571,7 +13573,7 @@
         <v>32</v>
       </c>
       <c r="D311" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E311">
         <v>0.14471827793029751</v>
@@ -13609,7 +13611,7 @@
         <v>32</v>
       </c>
       <c r="D312" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E312">
         <v>2.750595377297E-2</v>
@@ -13647,7 +13649,7 @@
         <v>32</v>
       </c>
       <c r="D313" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E313">
         <v>8.2471759147179885E-2</v>
@@ -13685,7 +13687,7 @@
         <v>32</v>
       </c>
       <c r="D314" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E314">
         <v>5.9658100647303022E-2</v>
@@ -13723,7 +13725,7 @@
         <v>32</v>
       </c>
       <c r="D315" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E315">
         <v>0.13137066656091501</v>
@@ -13761,7 +13763,7 @@
         <v>32</v>
       </c>
       <c r="D316" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -13799,7 +13801,7 @@
         <v>32</v>
       </c>
       <c r="D317" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E317">
         <v>2.6871715657817371E-17</v>
@@ -13837,7 +13839,7 @@
         <v>32</v>
       </c>
       <c r="D318" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E318">
         <v>1.0495912776773159E-16</v>
@@ -13875,7 +13877,7 @@
         <v>32</v>
       </c>
       <c r="D319" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E319">
         <v>6.1763455139221564E-18</v>
@@ -13913,7 +13915,7 @@
         <v>32</v>
       </c>
       <c r="D320" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E320">
         <v>1.3998486329548161E-2</v>
@@ -13951,7 +13953,7 @@
         <v>32</v>
       </c>
       <c r="D321" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E321">
         <v>1.4927572287598369E-17</v>
@@ -13989,7 +13991,7 @@
         <v>32</v>
       </c>
       <c r="D322" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -14027,7 +14029,7 @@
         <v>32</v>
       </c>
       <c r="D323" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E323">
         <v>9.3850552633837723E-19</v>
@@ -14065,7 +14067,7 @@
         <v>32</v>
       </c>
       <c r="D324" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -14103,7 +14105,7 @@
         <v>31</v>
       </c>
       <c r="D325" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E325">
         <v>0.11975572493127599</v>
@@ -14141,7 +14143,7 @@
         <v>31</v>
       </c>
       <c r="D326" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -14179,7 +14181,7 @@
         <v>31</v>
       </c>
       <c r="D327" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E327">
         <v>1.096878762494246E-2</v>
@@ -14217,7 +14219,7 @@
         <v>31</v>
       </c>
       <c r="D328" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E328">
         <v>3.0788585297119479E-2</v>
@@ -14255,7 +14257,7 @@
         <v>31</v>
       </c>
       <c r="D329" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E329">
         <v>0.36247284608664238</v>
@@ -14293,7 +14295,7 @@
         <v>31</v>
       </c>
       <c r="D330" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E330">
         <v>0.1041886471989386</v>
@@ -14331,7 +14333,7 @@
         <v>31</v>
       </c>
       <c r="D331" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E331">
         <v>9.1503255744474613E-2</v>
@@ -14369,7 +14371,7 @@
         <v>31</v>
       </c>
       <c r="D332" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E332">
         <v>2.4532898039952251E-2</v>
@@ -14407,7 +14409,7 @@
         <v>31</v>
       </c>
       <c r="D333" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E333">
         <v>7.3426404031484857E-2</v>
@@ -14445,7 +14447,7 @@
         <v>31</v>
       </c>
       <c r="D334" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E334">
         <v>1.8646334557568998E-2</v>
@@ -14483,7 +14485,7 @@
         <v>31</v>
       </c>
       <c r="D335" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E335">
         <v>0.14676590329890191</v>
@@ -14521,7 +14523,7 @@
         <v>31</v>
       </c>
       <c r="D336" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -14559,7 +14561,7 @@
         <v>31</v>
       </c>
       <c r="D337" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -14597,7 +14599,7 @@
         <v>31</v>
       </c>
       <c r="D338" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -14635,7 +14637,7 @@
         <v>31</v>
       </c>
       <c r="D339" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E339">
         <v>3.928159994018657E-18</v>
@@ -14673,7 +14675,7 @@
         <v>31</v>
       </c>
       <c r="D340" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E340">
         <v>1.6950613188698459E-2</v>
@@ -14711,7 +14713,7 @@
         <v>31</v>
       </c>
       <c r="D341" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E341">
         <v>0</v>
@@ -14749,7 +14751,7 @@
         <v>31</v>
       </c>
       <c r="D342" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E342">
         <v>0</v>
@@ -14787,7 +14789,7 @@
         <v>31</v>
       </c>
       <c r="D343" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E343">
         <v>2.410424352217861E-17</v>
@@ -14825,7 +14827,7 @@
         <v>32</v>
       </c>
       <c r="D344" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E344">
         <v>5.4794983181335417E-2</v>
@@ -14863,7 +14865,7 @@
         <v>32</v>
       </c>
       <c r="D345" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E345">
         <v>0.1248323559836277</v>
@@ -14901,7 +14903,7 @@
         <v>32</v>
       </c>
       <c r="D346" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E346">
         <v>9.5996847195963554E-3</v>
@@ -14939,7 +14941,7 @@
         <v>32</v>
       </c>
       <c r="D347" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E347">
         <v>5.5101659019445609E-2</v>
@@ -14977,7 +14979,7 @@
         <v>32</v>
       </c>
       <c r="D348" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E348">
         <v>0.26262628023607909</v>
@@ -15015,7 +15017,7 @@
         <v>32</v>
       </c>
       <c r="D349" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E349">
         <v>4.0606855058860462E-2</v>
@@ -15053,7 +15055,7 @@
         <v>32</v>
       </c>
       <c r="D350" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E350">
         <v>6.3205810532051057E-17</v>
@@ -15091,7 +15093,7 @@
         <v>32</v>
       </c>
       <c r="D351" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E351">
         <v>0</v>
@@ -15129,7 +15131,7 @@
         <v>32</v>
       </c>
       <c r="D352" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E352">
         <v>2.1430304976308512E-17</v>
@@ -15167,7 +15169,7 @@
         <v>32</v>
       </c>
       <c r="D353" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E353">
         <v>0</v>
@@ -15205,7 +15207,7 @@
         <v>32</v>
       </c>
       <c r="D354" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E354">
         <v>2.5295048822709942E-16</v>
@@ -15243,7 +15245,7 @@
         <v>32</v>
       </c>
       <c r="D355" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E355">
         <v>0</v>
@@ -15281,7 +15283,7 @@
         <v>32</v>
       </c>
       <c r="D356" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E356">
         <v>3.3144705149725477E-17</v>
@@ -15319,7 +15321,7 @@
         <v>32</v>
       </c>
       <c r="D357" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E357">
         <v>0.13173351027823951</v>
@@ -15357,7 +15359,7 @@
         <v>32</v>
       </c>
       <c r="D358" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E358">
         <v>0.20658117688504671</v>
@@ -15395,7 +15397,7 @@
         <v>32</v>
       </c>
       <c r="D359" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E359">
         <v>7.9404777967070225E-2</v>
@@ -15433,7 +15435,7 @@
         <v>32</v>
       </c>
       <c r="D360" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E360">
         <v>0</v>
@@ -15471,7 +15473,7 @@
         <v>32</v>
       </c>
       <c r="D361" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E361">
         <v>0</v>
@@ -15509,7 +15511,7 @@
         <v>32</v>
       </c>
       <c r="D362" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E362">
         <v>3.4718716670698618E-2</v>
@@ -15547,7 +15549,7 @@
         <v>31</v>
       </c>
       <c r="D363" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E363">
         <v>0</v>
@@ -15585,7 +15587,7 @@
         <v>31</v>
       </c>
       <c r="D364" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E364">
         <v>0.17008840748359519</v>
@@ -15623,7 +15625,7 @@
         <v>31</v>
       </c>
       <c r="D365" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E365">
         <v>0.24161629344841831</v>
@@ -15661,7 +15663,7 @@
         <v>31</v>
       </c>
       <c r="D366" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E366">
         <v>3.513812937027511E-15</v>
@@ -15699,7 +15701,7 @@
         <v>31</v>
       </c>
       <c r="D367" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E367">
         <v>6.3962081192613077E-15</v>
@@ -15737,7 +15739,7 @@
         <v>31</v>
       </c>
       <c r="D368" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E368">
         <v>5.9332028999259793E-15</v>
@@ -15775,7 +15777,7 @@
         <v>31</v>
       </c>
       <c r="D369" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E369">
         <v>5.0206926570599102E-3</v>
@@ -15813,7 +15815,7 @@
         <v>31</v>
       </c>
       <c r="D370" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E370">
         <v>0.1236023250322183</v>
@@ -15851,7 +15853,7 @@
         <v>31</v>
       </c>
       <c r="D371" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E371">
         <v>5.8723214953549887E-15</v>
@@ -15889,7 +15891,7 @@
         <v>31</v>
       </c>
       <c r="D372" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E372">
         <v>0.12520210133536319</v>
@@ -15927,7 +15929,7 @@
         <v>31</v>
       </c>
       <c r="D373" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E373">
         <v>0</v>
@@ -15965,7 +15967,7 @@
         <v>31</v>
       </c>
       <c r="D374" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E374">
         <v>8.109453335937193E-15</v>
@@ -16003,7 +16005,7 @@
         <v>31</v>
       </c>
       <c r="D375" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E375">
         <v>3.0812803108229568E-3</v>
@@ -16041,7 +16043,7 @@
         <v>31</v>
       </c>
       <c r="D376" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E376">
         <v>0.29264414334651578</v>
@@ -16079,7 +16081,7 @@
         <v>31</v>
       </c>
       <c r="D377" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E377">
         <v>1.8112258475393821E-3</v>
@@ -16117,7 +16119,7 @@
         <v>31</v>
       </c>
       <c r="D378" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E378">
         <v>9.4784176670686062E-16</v>
@@ -16155,7 +16157,7 @@
         <v>31</v>
       </c>
       <c r="D379" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E379">
         <v>3.6933530538424492E-2</v>
@@ -16193,7 +16195,7 @@
         <v>31</v>
       </c>
       <c r="D380" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E380">
         <v>5.6525243685890116E-15</v>
@@ -16231,7 +16233,7 @@
         <v>31</v>
       </c>
       <c r="D381" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E381">
         <v>6.0987251656211393E-15</v>
@@ -16269,7 +16271,7 @@
         <v>32</v>
       </c>
       <c r="D382" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E382">
         <v>6.7691695363420928E-2</v>
@@ -16307,7 +16309,7 @@
         <v>32</v>
       </c>
       <c r="D383" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E383">
         <v>0</v>
@@ -16345,7 +16347,7 @@
         <v>32</v>
       </c>
       <c r="D384" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E384">
         <v>2.8455322743627689E-2</v>
@@ -16383,7 +16385,7 @@
         <v>32</v>
       </c>
       <c r="D385" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E385">
         <v>2.5683418257820341E-2</v>
@@ -16421,7 +16423,7 @@
         <v>32</v>
       </c>
       <c r="D386" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E386">
         <v>1.4317230479850861E-2</v>
@@ -16459,7 +16461,7 @@
         <v>32</v>
       </c>
       <c r="D387" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E387">
         <v>0.14469431535806229</v>
@@ -16497,7 +16499,7 @@
         <v>32</v>
       </c>
       <c r="D388" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E388">
         <v>0</v>
@@ -16535,7 +16537,7 @@
         <v>32</v>
       </c>
       <c r="D389" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E389">
         <v>0</v>
@@ -16573,7 +16575,7 @@
         <v>32</v>
       </c>
       <c r="D390" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E390">
         <v>1.8008718429595151E-2</v>
@@ -16611,7 +16613,7 @@
         <v>32</v>
       </c>
       <c r="D391" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E391">
         <v>1.3727529421758781E-17</v>
@@ -16649,7 +16651,7 @@
         <v>32</v>
       </c>
       <c r="D392" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E392">
         <v>0</v>
@@ -16687,7 +16689,7 @@
         <v>32</v>
       </c>
       <c r="D393" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E393">
         <v>1.505647780653027E-2</v>
@@ -16725,7 +16727,7 @@
         <v>32</v>
       </c>
       <c r="D394" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E394">
         <v>0.24729600292416909</v>
@@ -16763,7 +16765,7 @@
         <v>32</v>
       </c>
       <c r="D395" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E395">
         <v>0.16490689168051861</v>
@@ -16801,7 +16803,7 @@
         <v>32</v>
       </c>
       <c r="D396" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E396">
         <v>0.13592499268904959</v>
@@ -16839,7 +16841,7 @@
         <v>32</v>
       </c>
       <c r="D397" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E397">
         <v>0.13796493426735509</v>
@@ -16877,7 +16879,7 @@
         <v>32</v>
       </c>
       <c r="D398" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E398">
         <v>0</v>
@@ -16915,7 +16917,7 @@
         <v>32</v>
       </c>
       <c r="D399" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E399">
         <v>1.208636814438775E-17</v>
@@ -16953,7 +16955,7 @@
         <v>32</v>
       </c>
       <c r="D400" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E400">
         <v>1.093493466663612E-16</v>
@@ -16991,7 +16993,7 @@
         <v>31</v>
       </c>
       <c r="D401" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E401">
         <v>3.7098911872132448E-2</v>
@@ -17029,7 +17031,7 @@
         <v>31</v>
       </c>
       <c r="D402" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E402">
         <v>5.095414517637456E-2</v>
@@ -17067,7 +17069,7 @@
         <v>31</v>
       </c>
       <c r="D403" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E403">
         <v>2.186742738295647E-2</v>
@@ -17105,7 +17107,7 @@
         <v>31</v>
       </c>
       <c r="D404" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E404">
         <v>0.14686572803727421</v>
@@ -17143,7 +17145,7 @@
         <v>31</v>
       </c>
       <c r="D405" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E405">
         <v>1.0573237818026601E-2</v>
@@ -17181,7 +17183,7 @@
         <v>31</v>
       </c>
       <c r="D406" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E406">
         <v>0</v>
@@ -17219,7 +17221,7 @@
         <v>31</v>
       </c>
       <c r="D407" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E407">
         <v>5.3862538820802072E-3</v>
@@ -17257,7 +17259,7 @@
         <v>31</v>
       </c>
       <c r="D408" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E408">
         <v>0.1712634887319707</v>
@@ -17295,7 +17297,7 @@
         <v>31</v>
       </c>
       <c r="D409" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E409">
         <v>8.6183172323331322E-2</v>
@@ -17333,7 +17335,7 @@
         <v>31</v>
       </c>
       <c r="D410" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E410">
         <v>0.19872241479570271</v>
@@ -17371,7 +17373,7 @@
         <v>31</v>
       </c>
       <c r="D411" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E411">
         <v>0</v>
@@ -17409,7 +17411,7 @@
         <v>31</v>
       </c>
       <c r="D412" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E412">
         <v>3.6029123946711192E-2</v>
@@ -17447,7 +17449,7 @@
         <v>31</v>
       </c>
       <c r="D413" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E413">
         <v>0</v>
@@ -17485,7 +17487,7 @@
         <v>31</v>
       </c>
       <c r="D414" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E414">
         <v>1.0848365115722821E-2</v>
@@ -17523,7 +17525,7 @@
         <v>31</v>
       </c>
       <c r="D415" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E415">
         <v>0.1164800899342313</v>
@@ -17561,7 +17563,7 @@
         <v>31</v>
       </c>
       <c r="D416" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E416">
         <v>0</v>
@@ -17599,7 +17601,7 @@
         <v>31</v>
       </c>
       <c r="D417" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E417">
         <v>0.1077276409834857</v>
@@ -17637,7 +17639,7 @@
         <v>31</v>
       </c>
       <c r="D418" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E418">
         <v>0</v>
@@ -17675,7 +17677,7 @@
         <v>31</v>
       </c>
       <c r="D419" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E419">
         <v>0</v>
@@ -17713,7 +17715,7 @@
         <v>32</v>
       </c>
       <c r="D420" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E420">
         <v>0</v>
@@ -17751,7 +17753,7 @@
         <v>32</v>
       </c>
       <c r="D421" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E421">
         <v>3.4959912349650887E-2</v>
@@ -17789,7 +17791,7 @@
         <v>32</v>
       </c>
       <c r="D422" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E422">
         <v>1.6631493198685369E-17</v>
@@ -17827,7 +17829,7 @@
         <v>32</v>
       </c>
       <c r="D423" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E423">
         <v>0.16025553157299721</v>
@@ -17865,7 +17867,7 @@
         <v>32</v>
       </c>
       <c r="D424" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E424">
         <v>1.6887465763077252E-2</v>
@@ -17903,7 +17905,7 @@
         <v>32</v>
       </c>
       <c r="D425" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E425">
         <v>0</v>
@@ -17941,7 +17943,7 @@
         <v>32</v>
       </c>
       <c r="D426" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E426">
         <v>3.8527306152576067E-2</v>
@@ -17979,7 +17981,7 @@
         <v>32</v>
       </c>
       <c r="D427" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E427">
         <v>9.0489622923473678E-2</v>
@@ -18017,7 +18019,7 @@
         <v>32</v>
       </c>
       <c r="D428" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E428">
         <v>0</v>
@@ -18055,7 +18057,7 @@
         <v>32</v>
       </c>
       <c r="D429" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E429">
         <v>7.5752563938018533E-2</v>
@@ -18093,7 +18095,7 @@
         <v>32</v>
       </c>
       <c r="D430" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E430">
         <v>0</v>
@@ -18131,7 +18133,7 @@
         <v>32</v>
       </c>
       <c r="D431" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E431">
         <v>4.8957974955706506E-16</v>
@@ -18169,7 +18171,7 @@
         <v>32</v>
       </c>
       <c r="D432" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E432">
         <v>0</v>
@@ -18207,7 +18209,7 @@
         <v>32</v>
       </c>
       <c r="D433" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E433">
         <v>2.1177233697702889E-2</v>
@@ -18245,7 +18247,7 @@
         <v>32</v>
       </c>
       <c r="D434" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E434">
         <v>0.36841257763383228</v>
@@ -18283,7 +18285,7 @@
         <v>32</v>
       </c>
       <c r="D435" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E435">
         <v>0.19353778596867061</v>
@@ -18321,7 +18323,7 @@
         <v>32</v>
       </c>
       <c r="D436" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E436">
         <v>0</v>
@@ -18359,7 +18361,7 @@
         <v>32</v>
       </c>
       <c r="D437" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E437">
         <v>0</v>
@@ -18397,7 +18399,7 @@
         <v>32</v>
       </c>
       <c r="D438" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E438">
         <v>0</v>
@@ -18435,7 +18437,7 @@
         <v>32</v>
       </c>
       <c r="D439" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E439">
         <v>9.9158947077231441E-2</v>
@@ -18473,7 +18475,7 @@
         <v>32</v>
       </c>
       <c r="D440" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E440">
         <v>4.0751132024034999E-2</v>
@@ -18511,7 +18513,7 @@
         <v>32</v>
       </c>
       <c r="D441" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E441">
         <v>3.6980122564867282E-3</v>
@@ -18549,7 +18551,7 @@
         <v>32</v>
       </c>
       <c r="D442" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E442">
         <v>0.3999999999999998</v>
@@ -18587,7 +18589,7 @@
         <v>32</v>
       </c>
       <c r="D443" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E443">
         <v>1.094295971656861E-2</v>
@@ -18625,7 +18627,7 @@
         <v>32</v>
       </c>
       <c r="D444" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E444">
         <v>4.7889184508810537E-2</v>
@@ -18663,7 +18665,7 @@
         <v>32</v>
       </c>
       <c r="D445" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E445">
         <v>1.7086772723566949E-17</v>
@@ -18701,7 +18703,7 @@
         <v>32</v>
       </c>
       <c r="D446" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E446">
         <v>0</v>
@@ -18739,7 +18741,7 @@
         <v>32</v>
       </c>
       <c r="D447" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E447">
         <v>2.8247808161757772E-17</v>
@@ -18777,7 +18779,7 @@
         <v>32</v>
       </c>
       <c r="D448" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E448">
         <v>6.1787017846852907E-2</v>
@@ -18815,7 +18817,7 @@
         <v>32</v>
       </c>
       <c r="D449" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E449">
         <v>0.1196103723100644</v>
@@ -18853,7 +18855,7 @@
         <v>32</v>
       </c>
       <c r="D450" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E450">
         <v>0</v>
@@ -18891,7 +18893,7 @@
         <v>32</v>
       </c>
       <c r="D451" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E451">
         <v>4.618765306915007E-18</v>
@@ -18929,7 +18931,7 @@
         <v>32</v>
       </c>
       <c r="D452" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E452">
         <v>0</v>
@@ -18967,7 +18969,7 @@
         <v>32</v>
       </c>
       <c r="D453" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E453">
         <v>0</v>
@@ -19005,7 +19007,7 @@
         <v>32</v>
       </c>
       <c r="D454" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E454">
         <v>0</v>
@@ -19043,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="D455" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E455">
         <v>0.20317052726901499</v>
@@ -19081,7 +19083,7 @@
         <v>32</v>
       </c>
       <c r="D456" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E456">
         <v>1.2991846990935561E-2</v>
@@ -19119,7 +19121,7 @@
         <v>32</v>
       </c>
       <c r="D457" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E457">
         <v>0</v>
@@ -19157,7 +19159,7 @@
         <v>31</v>
       </c>
       <c r="D458" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E458">
         <v>1.347633168496126E-17</v>
@@ -19195,7 +19197,7 @@
         <v>31</v>
       </c>
       <c r="D459" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E459">
         <v>1.591571477415181E-2</v>
@@ -19233,7 +19235,7 @@
         <v>31</v>
       </c>
       <c r="D460" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E460">
         <v>0</v>
@@ -19271,7 +19273,7 @@
         <v>31</v>
       </c>
       <c r="D461" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E461">
         <v>0</v>
@@ -19309,7 +19311,7 @@
         <v>31</v>
       </c>
       <c r="D462" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E462">
         <v>0.1544911721892826</v>
@@ -19347,7 +19349,7 @@
         <v>31</v>
       </c>
       <c r="D463" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E463">
         <v>0.20956526074372361</v>
@@ -19385,7 +19387,7 @@
         <v>31</v>
       </c>
       <c r="D464" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E464">
         <v>1.1959580212518161E-3</v>
@@ -19423,7 +19425,7 @@
         <v>31</v>
       </c>
       <c r="D465" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E465">
         <v>6.3402245978649768E-2</v>
@@ -19461,7 +19463,7 @@
         <v>31</v>
       </c>
       <c r="D466" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E466">
         <v>2.4921297494997609E-17</v>
@@ -19499,7 +19501,7 @@
         <v>31</v>
       </c>
       <c r="D467" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E467">
         <v>4.7403510662395273E-2</v>
@@ -19537,7 +19539,7 @@
         <v>31</v>
       </c>
       <c r="D468" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E468">
         <v>8.1836576031220271E-2</v>
@@ -19575,7 +19577,7 @@
         <v>31</v>
       </c>
       <c r="D469" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E469">
         <v>1.7249023553067962E-2</v>
@@ -19613,7 +19615,7 @@
         <v>31</v>
       </c>
       <c r="D470" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E470">
         <v>1.5244618841473019E-17</v>
@@ -19651,7 +19653,7 @@
         <v>31</v>
       </c>
       <c r="D471" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E471">
         <v>0.15538067977652689</v>
@@ -19689,7 +19691,7 @@
         <v>31</v>
       </c>
       <c r="D472" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E472">
         <v>1.4973858078217139E-17</v>
@@ -19727,7 +19729,7 @@
         <v>31</v>
       </c>
       <c r="D473" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E473">
         <v>0.2117090355408561</v>
@@ -19765,7 +19767,7 @@
         <v>31</v>
       </c>
       <c r="D474" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E474">
         <v>3.377602354433492E-2</v>
@@ -19803,7 +19805,7 @@
         <v>31</v>
       </c>
       <c r="D475" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E475">
         <v>8.0747991845388917E-3</v>
@@ -19841,7 +19843,7 @@
         <v>31</v>
       </c>
       <c r="D476" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E476">
         <v>0</v>
@@ -19879,7 +19881,7 @@
         <v>31</v>
       </c>
       <c r="D477" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E477">
         <v>1.21195963101568E-17</v>
@@ -19917,7 +19919,7 @@
         <v>31</v>
       </c>
       <c r="D478" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E478">
         <v>5.7412557886479204E-17</v>
@@ -19955,7 +19957,7 @@
         <v>31</v>
       </c>
       <c r="D479" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E479">
         <v>0</v>
@@ -19993,7 +19995,7 @@
         <v>31</v>
       </c>
       <c r="D480" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E480">
         <v>0.21878116730905739</v>
@@ -20031,7 +20033,7 @@
         <v>31</v>
       </c>
       <c r="D481" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E481">
         <v>4.2188743989575152E-2</v>
@@ -20069,7 +20071,7 @@
         <v>31</v>
       </c>
       <c r="D482" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E482">
         <v>7.5027384168536479E-2</v>
@@ -20107,7 +20109,7 @@
         <v>31</v>
       </c>
       <c r="D483" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E483">
         <v>2.8694577324257302E-17</v>
@@ -20145,7 +20147,7 @@
         <v>31</v>
       </c>
       <c r="D484" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E484">
         <v>4.6703680292357233E-2</v>
@@ -20183,7 +20185,7 @@
         <v>31</v>
       </c>
       <c r="D485" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E485">
         <v>2.0887440821071711E-17</v>
@@ -20221,7 +20223,7 @@
         <v>31</v>
       </c>
       <c r="D486" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E486">
         <v>2.970277327530329E-17</v>
@@ -20259,7 +20261,7 @@
         <v>31</v>
       </c>
       <c r="D487" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E487">
         <v>0</v>
@@ -20297,7 +20299,7 @@
         <v>31</v>
       </c>
       <c r="D488" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E488">
         <v>6.9527102787709572E-2</v>
@@ -20335,7 +20337,7 @@
         <v>31</v>
       </c>
       <c r="D489" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E489">
         <v>0</v>
@@ -20373,7 +20375,7 @@
         <v>31</v>
       </c>
       <c r="D490" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E490">
         <v>0</v>
@@ -20411,7 +20413,7 @@
         <v>31</v>
       </c>
       <c r="D491" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E491">
         <v>1.9404225531207092E-18</v>
@@ -20449,7 +20451,7 @@
         <v>31</v>
       </c>
       <c r="D492" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E492">
         <v>0.39432325023712272</v>
@@ -20487,7 +20489,7 @@
         <v>31</v>
       </c>
       <c r="D493" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E493">
         <v>1.8543140902851071E-2</v>
@@ -20525,7 +20527,7 @@
         <v>31</v>
       </c>
       <c r="D494" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E494">
         <v>4.9595702410071439E-17</v>
@@ -20563,7 +20565,7 @@
         <v>31</v>
       </c>
       <c r="D495" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E495">
         <v>0.13490553031279029</v>
@@ -20601,7 +20603,7 @@
         <v>32</v>
       </c>
       <c r="D496" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E496">
         <v>2.7300649519464931E-17</v>
@@ -20639,7 +20641,7 @@
         <v>32</v>
       </c>
       <c r="D497" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E497">
         <v>3.4088759950008668E-17</v>
@@ -20677,7 +20679,7 @@
         <v>32</v>
       </c>
       <c r="D498" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E498">
         <v>4.4392842580979842E-2</v>
@@ -20715,7 +20717,7 @@
         <v>32</v>
       </c>
       <c r="D499" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E499">
         <v>0</v>
@@ -20753,7 +20755,7 @@
         <v>32</v>
       </c>
       <c r="D500" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E500">
         <v>0.31839540715571779</v>
@@ -20791,7 +20793,7 @@
         <v>32</v>
       </c>
       <c r="D501" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E501">
         <v>2.6784174165349609E-17</v>
@@ -20829,7 +20831,7 @@
         <v>32</v>
       </c>
       <c r="D502" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E502">
         <v>0.13244342711133339</v>
@@ -20867,7 +20869,7 @@
         <v>32</v>
       </c>
       <c r="D503" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E503">
         <v>0</v>
@@ -20905,7 +20907,7 @@
         <v>32</v>
       </c>
       <c r="D504" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E504">
         <v>3.990630710866053E-17</v>
@@ -20943,7 +20945,7 @@
         <v>32</v>
       </c>
       <c r="D505" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E505">
         <v>0</v>
@@ -20981,7 +20983,7 @@
         <v>32</v>
       </c>
       <c r="D506" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E506">
         <v>0.32155615949169009</v>
@@ -21019,7 +21021,7 @@
         <v>32</v>
       </c>
       <c r="D507" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E507">
         <v>0</v>
@@ -21057,7 +21059,7 @@
         <v>32</v>
       </c>
       <c r="D508" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E508">
         <v>1.823101513558368E-19</v>
@@ -21095,7 +21097,7 @@
         <v>32</v>
       </c>
       <c r="D509" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E509">
         <v>0.18321216366027879</v>
@@ -21133,7 +21135,7 @@
         <v>32</v>
       </c>
       <c r="D510" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E510">
         <v>2.970645619052797E-17</v>
@@ -21171,7 +21173,7 @@
         <v>32</v>
       </c>
       <c r="D511" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E511">
         <v>0</v>
@@ -21209,7 +21211,7 @@
         <v>32</v>
       </c>
       <c r="D512" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E512">
         <v>9.3692907152211682E-19</v>
@@ -21247,7 +21249,7 @@
         <v>32</v>
       </c>
       <c r="D513" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E513">
         <v>0</v>
@@ -21285,7 +21287,7 @@
         <v>32</v>
       </c>
       <c r="D514" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E514">
         <v>0</v>
@@ -21323,7 +21325,7 @@
         <v>31</v>
       </c>
       <c r="D515" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E515">
         <v>0</v>
@@ -21361,7 +21363,7 @@
         <v>31</v>
       </c>
       <c r="D516" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E516">
         <v>3.559426494580363E-2</v>
@@ -21399,7 +21401,7 @@
         <v>31</v>
       </c>
       <c r="D517" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E517">
         <v>0</v>
@@ -21437,7 +21439,7 @@
         <v>31</v>
       </c>
       <c r="D518" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E518">
         <v>1.7087195644961001E-17</v>
@@ -21475,7 +21477,7 @@
         <v>31</v>
       </c>
       <c r="D519" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E519">
         <v>0</v>
@@ -21513,7 +21515,7 @@
         <v>31</v>
       </c>
       <c r="D520" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E520">
         <v>0.4</v>
@@ -21551,7 +21553,7 @@
         <v>31</v>
       </c>
       <c r="D521" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E521">
         <v>2.4548077307762178E-2</v>
@@ -21589,7 +21591,7 @@
         <v>31</v>
       </c>
       <c r="D522" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E522">
         <v>6.8117730413188938E-3</v>
@@ -21627,7 +21629,7 @@
         <v>31</v>
       </c>
       <c r="D523" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E523">
         <v>0</v>
@@ -21665,7 +21667,7 @@
         <v>31</v>
       </c>
       <c r="D524" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E524">
         <v>0</v>
@@ -21703,7 +21705,7 @@
         <v>31</v>
       </c>
       <c r="D525" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E525">
         <v>0</v>
@@ -21741,7 +21743,7 @@
         <v>31</v>
       </c>
       <c r="D526" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E526">
         <v>0.28928109748245762</v>
@@ -21779,7 +21781,7 @@
         <v>31</v>
       </c>
       <c r="D527" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E527">
         <v>8.1964868952517891E-17</v>
@@ -21817,7 +21819,7 @@
         <v>31</v>
       </c>
       <c r="D528" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E528">
         <v>4.7025910077224967E-2</v>
@@ -21855,7 +21857,7 @@
         <v>31</v>
       </c>
       <c r="D529" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E529">
         <v>0.103702299685306</v>
@@ -21893,7 +21895,7 @@
         <v>31</v>
       </c>
       <c r="D530" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E530">
         <v>0</v>
@@ -21931,7 +21933,7 @@
         <v>31</v>
       </c>
       <c r="D531" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E531">
         <v>9.3036577460126529E-2</v>
@@ -21969,7 +21971,7 @@
         <v>31</v>
       </c>
       <c r="D532" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E532">
         <v>1.9296257571400219E-17</v>
@@ -22007,7 +22009,7 @@
         <v>31</v>
       </c>
       <c r="D533" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E533">
         <v>8.1188139739885697E-17</v>
@@ -22045,7 +22047,7 @@
         <v>32</v>
       </c>
       <c r="D534" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E534">
         <v>3.0320513523366231E-18</v>
@@ -22083,7 +22085,7 @@
         <v>32</v>
       </c>
       <c r="D535" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E535">
         <v>0</v>
@@ -22121,7 +22123,7 @@
         <v>32</v>
       </c>
       <c r="D536" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E536">
         <v>5.639755542415118E-17</v>
@@ -22159,7 +22161,7 @@
         <v>32</v>
       </c>
       <c r="D537" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E537">
         <v>3.0680301463187769E-2</v>
@@ -22197,7 +22199,7 @@
         <v>32</v>
       </c>
       <c r="D538" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E538">
         <v>0</v>
@@ -22235,7 +22237,7 @@
         <v>32</v>
       </c>
       <c r="D539" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E539">
         <v>1.0035319760235181E-17</v>
@@ -22273,7 +22275,7 @@
         <v>32</v>
       </c>
       <c r="D540" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E540">
         <v>4.3095750020469647E-17</v>
@@ -22311,7 +22313,7 @@
         <v>32</v>
       </c>
       <c r="D541" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E541">
         <v>0.18053827930052649</v>
@@ -22349,7 +22351,7 @@
         <v>32</v>
       </c>
       <c r="D542" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E542">
         <v>0</v>
@@ -22387,7 +22389,7 @@
         <v>32</v>
       </c>
       <c r="D543" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E543">
         <v>4.4529728088995683E-18</v>
@@ -22425,7 +22427,7 @@
         <v>32</v>
       </c>
       <c r="D544" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E544">
         <v>0</v>
@@ -22463,7 +22465,7 @@
         <v>32</v>
       </c>
       <c r="D545" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E545">
         <v>0</v>
@@ -22501,7 +22503,7 @@
         <v>32</v>
       </c>
       <c r="D546" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E546">
         <v>4.6339478478388238E-17</v>
@@ -22539,7 +22541,7 @@
         <v>32</v>
       </c>
       <c r="D547" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E547">
         <v>2.9435762384147662E-17</v>
@@ -22577,7 +22579,7 @@
         <v>32</v>
       </c>
       <c r="D548" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E548">
         <v>0.32010016113983519</v>
@@ -22615,7 +22617,7 @@
         <v>32</v>
       </c>
       <c r="D549" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E549">
         <v>0</v>
@@ -22653,7 +22655,7 @@
         <v>32</v>
       </c>
       <c r="D550" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E550">
         <v>0</v>
@@ -22691,7 +22693,7 @@
         <v>32</v>
       </c>
       <c r="D551" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E551">
         <v>0.15841015901208949</v>
@@ -22729,7 +22731,7 @@
         <v>32</v>
       </c>
       <c r="D552" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E552">
         <v>0.31027109908436068</v>
@@ -22767,7 +22769,7 @@
         <v>31</v>
       </c>
       <c r="D553" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E553">
         <v>2.5327932709785231E-17</v>
@@ -22805,7 +22807,7 @@
         <v>31</v>
       </c>
       <c r="D554" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E554">
         <v>1.557476666381085E-2</v>
@@ -22843,7 +22845,7 @@
         <v>31</v>
       </c>
       <c r="D555" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E555">
         <v>1.1910930825277111E-17</v>
@@ -22881,7 +22883,7 @@
         <v>31</v>
       </c>
       <c r="D556" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E556">
         <v>1.015791082158206E-16</v>
@@ -22919,7 +22921,7 @@
         <v>31</v>
       </c>
       <c r="D557" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E557">
         <v>0</v>
@@ -22957,7 +22959,7 @@
         <v>31</v>
       </c>
       <c r="D558" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E558">
         <v>0</v>
@@ -22995,7 +22997,7 @@
         <v>31</v>
       </c>
       <c r="D559" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E559">
         <v>0.207890929980136</v>
@@ -23033,7 +23035,7 @@
         <v>31</v>
       </c>
       <c r="D560" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E560">
         <v>7.7627277024937422E-2</v>
@@ -23071,7 +23073,7 @@
         <v>31</v>
       </c>
       <c r="D561" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E561">
         <v>0</v>
@@ -23109,7 +23111,7 @@
         <v>31</v>
       </c>
       <c r="D562" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E562">
         <v>0</v>
@@ -23147,7 +23149,7 @@
         <v>31</v>
       </c>
       <c r="D563" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E563">
         <v>0</v>
@@ -23185,7 +23187,7 @@
         <v>31</v>
       </c>
       <c r="D564" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E564">
         <v>0</v>
@@ -23223,7 +23225,7 @@
         <v>31</v>
       </c>
       <c r="D565" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E565">
         <v>9.8170141854759196E-2</v>
@@ -23261,7 +23263,7 @@
         <v>31</v>
       </c>
       <c r="D566" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E566">
         <v>0.24627487354321781</v>
@@ -23299,7 +23301,7 @@
         <v>31</v>
       </c>
       <c r="D567" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E567">
         <v>0.20993382614201861</v>
@@ -23337,7 +23339,7 @@
         <v>31</v>
       </c>
       <c r="D568" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E568">
         <v>0</v>
@@ -23375,7 +23377,7 @@
         <v>31</v>
       </c>
       <c r="D569" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E569">
         <v>0.14452818479112001</v>
@@ -23413,7 +23415,7 @@
         <v>31</v>
       </c>
       <c r="D570" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E570">
         <v>1.715406476878123E-17</v>
@@ -23451,7 +23453,7 @@
         <v>31</v>
       </c>
       <c r="D571" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E571">
         <v>1.240009755767442E-18</v>
@@ -23489,7 +23491,7 @@
         <v>32</v>
       </c>
       <c r="D572" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E572">
         <v>3.5955392065874899E-17</v>
@@ -23527,7 +23529,7 @@
         <v>32</v>
       </c>
       <c r="D573" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E573">
         <v>7.671800561954083E-17</v>
@@ -23565,7 +23567,7 @@
         <v>32</v>
       </c>
       <c r="D574" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E574">
         <v>7.6946704515299491E-17</v>
@@ -23603,7 +23605,7 @@
         <v>32</v>
       </c>
       <c r="D575" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E575">
         <v>0</v>
@@ -23641,7 +23643,7 @@
         <v>32</v>
       </c>
       <c r="D576" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E576">
         <v>0.2265421948166004</v>
@@ -23679,7 +23681,7 @@
         <v>32</v>
       </c>
       <c r="D577" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E577">
         <v>0.11634991319626881</v>
@@ -23717,7 +23719,7 @@
         <v>32</v>
       </c>
       <c r="D578" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E578">
         <v>0</v>
@@ -23755,7 +23757,7 @@
         <v>32</v>
       </c>
       <c r="D579" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E579">
         <v>6.8741412171835756E-2</v>
@@ -23793,7 +23795,7 @@
         <v>32</v>
       </c>
       <c r="D580" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E580">
         <v>8.3123323737085614E-2</v>
@@ -23831,7 +23833,7 @@
         <v>32</v>
       </c>
       <c r="D581" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E581">
         <v>1.001870570012386E-17</v>
@@ -23869,7 +23871,7 @@
         <v>32</v>
       </c>
       <c r="D582" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E582">
         <v>0</v>
@@ -23907,7 +23909,7 @@
         <v>32</v>
       </c>
       <c r="D583" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E583">
         <v>0</v>
@@ -23945,7 +23947,7 @@
         <v>32</v>
       </c>
       <c r="D584" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E584">
         <v>0</v>
@@ -23983,7 +23985,7 @@
         <v>32</v>
       </c>
       <c r="D585" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E585">
         <v>0</v>
@@ -24021,7 +24023,7 @@
         <v>32</v>
       </c>
       <c r="D586" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E586">
         <v>0</v>
@@ -24059,7 +24061,7 @@
         <v>32</v>
       </c>
       <c r="D587" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E587">
         <v>0</v>
@@ -24097,7 +24099,7 @@
         <v>32</v>
       </c>
       <c r="D588" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E588">
         <v>0</v>
@@ -24135,7 +24137,7 @@
         <v>32</v>
       </c>
       <c r="D589" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E589">
         <v>0.36403762792998812</v>
@@ -24173,7 +24175,7 @@
         <v>32</v>
       </c>
       <c r="D590" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E590">
         <v>0.14120552814822121</v>
@@ -24211,7 +24213,7 @@
         <v>31</v>
       </c>
       <c r="D591" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E591">
         <v>0</v>
@@ -24249,7 +24251,7 @@
         <v>31</v>
       </c>
       <c r="D592" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E592">
         <v>0</v>
@@ -24287,7 +24289,7 @@
         <v>31</v>
       </c>
       <c r="D593" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E593">
         <v>0</v>
@@ -24325,7 +24327,7 @@
         <v>31</v>
       </c>
       <c r="D594" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E594">
         <v>0</v>
@@ -24363,7 +24365,7 @@
         <v>31</v>
       </c>
       <c r="D595" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E595">
         <v>0</v>
@@ -24401,7 +24403,7 @@
         <v>31</v>
       </c>
       <c r="D596" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E596">
         <v>4.8428756199391412E-17</v>
@@ -24439,7 +24441,7 @@
         <v>31</v>
       </c>
       <c r="D597" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E597">
         <v>0</v>
@@ -24477,7 +24479,7 @@
         <v>31</v>
       </c>
       <c r="D598" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E598">
         <v>0.11623756131183589</v>
@@ -24515,7 +24517,7 @@
         <v>31</v>
       </c>
       <c r="D599" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E599">
         <v>0.19707393098228521</v>
@@ -24553,7 +24555,7 @@
         <v>31</v>
       </c>
       <c r="D600" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E600">
         <v>0.1830363052617576</v>
@@ -24591,7 +24593,7 @@
         <v>31</v>
       </c>
       <c r="D601" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E601">
         <v>2.719087758110788E-18</v>
@@ -24629,7 +24631,7 @@
         <v>31</v>
       </c>
       <c r="D602" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E602">
         <v>0</v>
@@ -24667,7 +24669,7 @@
         <v>31</v>
       </c>
       <c r="D603" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E603">
         <v>9.7221024504055661E-2</v>
@@ -24705,7 +24707,7 @@
         <v>31</v>
       </c>
       <c r="D604" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E604">
         <v>0.10561969260276401</v>
@@ -24743,7 +24745,7 @@
         <v>31</v>
       </c>
       <c r="D605" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E605">
         <v>2.6830888578524799E-18</v>
@@ -24781,7 +24783,7 @@
         <v>31</v>
       </c>
       <c r="D606" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E606">
         <v>2.1747682918178639E-17</v>
@@ -24819,7 +24821,7 @@
         <v>31</v>
       </c>
       <c r="D607" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E607">
         <v>2.180612819153918E-17</v>
@@ -24857,7 +24859,7 @@
         <v>31</v>
       </c>
       <c r="D608" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E608">
         <v>0.30081148533730151</v>
@@ -24895,7 +24897,7 @@
         <v>31</v>
       </c>
       <c r="D609" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E609">
         <v>0</v>
@@ -24933,7 +24935,7 @@
         <v>32</v>
       </c>
       <c r="D610" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E610">
         <v>0</v>
@@ -24971,7 +24973,7 @@
         <v>32</v>
       </c>
       <c r="D611" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E611">
         <v>0</v>
@@ -25009,7 +25011,7 @@
         <v>32</v>
       </c>
       <c r="D612" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E612">
         <v>0</v>
@@ -25047,7 +25049,7 @@
         <v>32</v>
       </c>
       <c r="D613" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E613">
         <v>5.5525858888001108E-2</v>
@@ -25085,7 +25087,7 @@
         <v>32</v>
       </c>
       <c r="D614" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E614">
         <v>0</v>
@@ -25123,7 +25125,7 @@
         <v>32</v>
       </c>
       <c r="D615" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E615">
         <v>0</v>
@@ -25161,7 +25163,7 @@
         <v>32</v>
       </c>
       <c r="D616" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E616">
         <v>8.0122229689308095E-18</v>
@@ -25199,7 +25201,7 @@
         <v>32</v>
       </c>
       <c r="D617" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E617">
         <v>0</v>
@@ -25237,7 +25239,7 @@
         <v>32</v>
       </c>
       <c r="D618" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E618">
         <v>8.8154751130309224E-17</v>
@@ -25275,7 +25277,7 @@
         <v>32</v>
       </c>
       <c r="D619" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E619">
         <v>0.22355438848191631</v>
@@ -25313,7 +25315,7 @@
         <v>32</v>
       </c>
       <c r="D620" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E620">
         <v>2.0885511106894732E-2</v>
@@ -25351,7 +25353,7 @@
         <v>32</v>
       </c>
       <c r="D621" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E621">
         <v>0.20470683877322199</v>
@@ -25389,7 +25391,7 @@
         <v>32</v>
       </c>
       <c r="D622" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E622">
         <v>3.7027906532033608E-17</v>
@@ -25427,7 +25429,7 @@
         <v>32</v>
       </c>
       <c r="D623" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E623">
         <v>0</v>
@@ -25465,7 +25467,7 @@
         <v>32</v>
       </c>
       <c r="D624" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E624">
         <v>3.6271020894412663E-2</v>
@@ -25503,7 +25505,7 @@
         <v>32</v>
       </c>
       <c r="D625" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E625">
         <v>2.3766180596466389E-17</v>
@@ -25541,7 +25543,7 @@
         <v>32</v>
       </c>
       <c r="D626" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E626">
         <v>0.13684526692886109</v>
@@ -25579,7 +25581,7 @@
         <v>32</v>
       </c>
       <c r="D627" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E627">
         <v>0.21601289185657599</v>
@@ -25617,7 +25619,7 @@
         <v>32</v>
       </c>
       <c r="D628" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E628">
         <v>0.10619822307011589</v>
@@ -25655,7 +25657,7 @@
         <v>31</v>
       </c>
       <c r="D629" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E629">
         <v>2.2595978954746031E-17</v>
@@ -25693,7 +25695,7 @@
         <v>31</v>
       </c>
       <c r="D630" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E630">
         <v>0</v>
@@ -25731,7 +25733,7 @@
         <v>31</v>
       </c>
       <c r="D631" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E631">
         <v>0</v>
@@ -25769,7 +25771,7 @@
         <v>31</v>
       </c>
       <c r="D632" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E632">
         <v>6.5924417370390967E-2</v>
@@ -25807,7 +25809,7 @@
         <v>31</v>
       </c>
       <c r="D633" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E633">
         <v>6.8610769547223978E-18</v>
@@ -25845,7 +25847,7 @@
         <v>31</v>
       </c>
       <c r="D634" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E634">
         <v>0.2058940735322955</v>
@@ -25883,7 +25885,7 @@
         <v>31</v>
       </c>
       <c r="D635" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E635">
         <v>0</v>
@@ -25921,7 +25923,7 @@
         <v>31</v>
       </c>
       <c r="D636" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E636">
         <v>1.993044621507534E-2</v>
@@ -25959,7 +25961,7 @@
         <v>31</v>
       </c>
       <c r="D637" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E637">
         <v>7.9262036524000268E-2</v>
@@ -25997,7 +25999,7 @@
         <v>31</v>
       </c>
       <c r="D638" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E638">
         <v>3.1560660654160702E-2</v>
@@ -26035,7 +26037,7 @@
         <v>31</v>
       </c>
       <c r="D639" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E639">
         <v>9.099475978018827E-2</v>
@@ -26073,7 +26075,7 @@
         <v>31</v>
       </c>
       <c r="D640" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E640">
         <v>0</v>
@@ -26111,7 +26113,7 @@
         <v>31</v>
       </c>
       <c r="D641" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E641">
         <v>0</v>
@@ -26149,7 +26151,7 @@
         <v>31</v>
       </c>
       <c r="D642" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E642">
         <v>2.9879588671704543E-17</v>
@@ -26187,7 +26189,7 @@
         <v>31</v>
       </c>
       <c r="D643" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E643">
         <v>3.8695980734037681E-17</v>
@@ -26225,7 +26227,7 @@
         <v>31</v>
       </c>
       <c r="D644" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E644">
         <v>0.1753404455277239</v>
@@ -26263,7 +26265,7 @@
         <v>31</v>
       </c>
       <c r="D645" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E645">
         <v>0.25713599581632768</v>
@@ -26301,7 +26303,7 @@
         <v>31</v>
       </c>
       <c r="D646" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E646">
         <v>7.3957164579837198E-2</v>
@@ -26339,7 +26341,7 @@
         <v>31</v>
       </c>
       <c r="D647" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E647">
         <v>1.0086440063074091E-18</v>
@@ -26377,7 +26379,7 @@
         <v>32</v>
       </c>
       <c r="D648" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E648">
         <v>2.4604104425561401E-17</v>
@@ -26415,7 +26417,7 @@
         <v>32</v>
       </c>
       <c r="D649" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E649">
         <v>0.22132892009546071</v>
@@ -26453,7 +26455,7 @@
         <v>32</v>
       </c>
       <c r="D650" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E650">
         <v>0</v>
@@ -26491,7 +26493,7 @@
         <v>32</v>
       </c>
       <c r="D651" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E651">
         <v>1.6296493223828531E-2</v>
@@ -26529,7 +26531,7 @@
         <v>32</v>
       </c>
       <c r="D652" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E652">
         <v>7.552187853318447E-18</v>
@@ -26567,7 +26569,7 @@
         <v>32</v>
       </c>
       <c r="D653" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E653">
         <v>4.3635479411718359E-2</v>
@@ -26605,7 +26607,7 @@
         <v>32</v>
       </c>
       <c r="D654" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E654">
         <v>0</v>
@@ -26643,7 +26645,7 @@
         <v>32</v>
       </c>
       <c r="D655" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E655">
         <v>0</v>
@@ -26681,7 +26683,7 @@
         <v>32</v>
       </c>
       <c r="D656" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E656">
         <v>6.119898285874607E-17</v>
@@ -26719,7 +26721,7 @@
         <v>32</v>
       </c>
       <c r="D657" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E657">
         <v>0</v>
@@ -26757,7 +26759,7 @@
         <v>32</v>
       </c>
       <c r="D658" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E658">
         <v>0</v>
@@ -26795,7 +26797,7 @@
         <v>32</v>
       </c>
       <c r="D659" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E659">
         <v>0</v>
@@ -26833,7 +26835,7 @@
         <v>32</v>
       </c>
       <c r="D660" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E660">
         <v>4.0252163806391462E-18</v>
@@ -26871,7 +26873,7 @@
         <v>32</v>
       </c>
       <c r="D661" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E661">
         <v>2.1634389253385559E-2</v>
@@ -26909,7 +26911,7 @@
         <v>32</v>
       </c>
       <c r="D662" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E662">
         <v>5.9689057075837278E-2</v>
@@ -26947,7 +26949,7 @@
         <v>32</v>
       </c>
       <c r="D663" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E663">
         <v>0.39352516816008598</v>
@@ -26985,7 +26987,7 @@
         <v>32</v>
       </c>
       <c r="D664" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E664">
         <v>4.497049984714032E-2</v>
@@ -27023,7 +27025,7 @@
         <v>32</v>
       </c>
       <c r="D665" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E665">
         <v>0</v>
@@ -27061,7 +27063,7 @@
         <v>32</v>
       </c>
       <c r="D666" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E666">
         <v>0.1989199929325432</v>
@@ -27101,22 +27103,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -27136,7 +27138,7 @@
         <v>-7.5233562600774961E-3</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -27156,7 +27158,7 @@
         <v>4.695610122698568E-2</v>
       </c>
       <c r="F3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -27176,7 +27178,7 @@
         <v>1.875619976022325E-2</v>
       </c>
       <c r="F4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -27196,7 +27198,7 @@
         <v>0.17150769087796741</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -27216,7 +27218,7 @@
         <v>9.696393659562097E-2</v>
       </c>
       <c r="F6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -27236,7 +27238,7 @@
         <v>-2.062781518686951E-2</v>
       </c>
       <c r="F7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -27256,7 +27258,7 @@
         <v>1.3189192358239231E-2</v>
       </c>
       <c r="F8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -27276,7 +27278,7 @@
         <v>-5.2069997865027418E-3</v>
       </c>
       <c r="F9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -27296,7 +27298,7 @@
         <v>-1.6455262974022781E-2</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -27316,7 +27318,7 @@
         <v>6.4790508392178925E-2</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -27336,7 +27338,7 @@
         <v>6.3453233349120897E-2</v>
       </c>
       <c r="F12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -27356,7 +27358,7 @@
         <v>7.8649047104800029E-2</v>
       </c>
       <c r="F13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -27376,7 +27378,7 @@
         <v>0.11419418219286651</v>
       </c>
       <c r="F14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -27396,7 +27398,7 @@
         <v>1.2973505787085671E-2</v>
       </c>
       <c r="F15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -27416,7 +27418,7 @@
         <v>5.6574291047037713E-2</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -27436,7 +27438,7 @@
         <v>1.447037563918285E-2</v>
       </c>
       <c r="F17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -27456,7 +27458,7 @@
         <v>2.419117187809228E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -27476,7 +27478,7 @@
         <v>4.58736913289155E-2</v>
       </c>
       <c r="F19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -27496,7 +27498,7 @@
         <v>2.433424552614882E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -27516,7 +27518,7 @@
         <v>4.7812162544266901E-2</v>
       </c>
       <c r="F21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -27536,7 +27538,7 @@
         <v>-1.2966413972361529E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -27556,7 +27558,7 @@
         <v>-5.2841626469383174E-3</v>
       </c>
       <c r="F23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -27576,7 +27578,7 @@
         <v>1.7747936319294281E-2</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -27596,7 +27598,7 @@
         <v>3.4132549955070419E-3</v>
       </c>
       <c r="F25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -27616,7 +27618,7 @@
         <v>-2.0863516664033521E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -27636,7 +27638,7 @@
         <v>2.039268878706291E-2</v>
       </c>
       <c r="F27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -27656,7 +27658,7 @@
         <v>0.111488625795906</v>
       </c>
       <c r="F28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -27676,7 +27678,7 @@
         <v>9.1810653874379478E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -27696,7 +27698,7 @@
         <v>9.3639283762112946E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -27716,7 +27718,7 @@
         <v>3.021853191719304E-2</v>
       </c>
       <c r="F31" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -27736,7 +27738,7 @@
         <v>6.4937987846271028E-2</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -27756,7 +27758,7 @@
         <v>7.7419327544185235E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -27776,7 +27778,7 @@
         <v>6.1540169705672998E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -27796,7 +27798,7 @@
         <v>5.2658681076400933E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -27816,7 +27818,7 @@
         <v>0.25802807693952529</v>
       </c>
       <c r="F36" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
